--- a/excel_routes/route_HMB_RUH_threats.xlsx
+++ b/excel_routes/route_HMB_RUH_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD49BE8-E761-4A7C-A948-250E535E9EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCED3ED-CF1C-40E6-B70A-E6AB0DAB6531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -60,126 +60,123 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>27-JUL-26</t>
+    <t>30-JUL-26</t>
   </si>
   <si>
     <t>SM-463</t>
   </si>
   <si>
+    <t>Nile Air NP-251</t>
+  </si>
+  <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>Nile Air NP-151</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-162</t>
+  </si>
+  <si>
+    <t>03-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-153</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-649</t>
+  </si>
+  <si>
+    <t>06-AUG-26</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>10-AUG-26</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-415</t>
+  </si>
+  <si>
+    <t>13-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-255</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-689</t>
+  </si>
+  <si>
+    <t>17-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-453</t>
+  </si>
+  <si>
+    <t>20-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-455</t>
+  </si>
+  <si>
+    <t>24-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-351</t>
+  </si>
+  <si>
+    <t>27-AUG-26</t>
+  </si>
+  <si>
     <t>Nesma Airlines NE-160</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>30-JUL-26</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>Nile Air NP-251</t>
+    <t>Nile Air NP-353</t>
+  </si>
+  <si>
+    <t>31-AUG-26</t>
+  </si>
+  <si>
+    <t>03-SEP-26</t>
+  </si>
+  <si>
+    <t>flyadeal F3-608</t>
+  </si>
+  <si>
+    <t>flyadeal F3-606</t>
+  </si>
+  <si>
+    <t>flyadeal F3-614</t>
+  </si>
+  <si>
+    <t>flynas XY-280</t>
+  </si>
+  <si>
+    <t>07-SEP-26</t>
   </si>
   <si>
     <t>EgyptAir MS-651</t>
   </si>
   <si>
-    <t>03-AUG-26</t>
-  </si>
-  <si>
-    <t>flynas XY-266</t>
-  </si>
-  <si>
-    <t>flynas XY-288</t>
+    <t>10-SEP-26</t>
+  </si>
+  <si>
+    <t>14-SEP-26</t>
+  </si>
+  <si>
+    <t>flynas XY-274</t>
   </si>
   <si>
     <t>flynas XY-272</t>
   </si>
   <si>
-    <t>06-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-153</t>
-  </si>
-  <si>
-    <t>MED</t>
-  </si>
-  <si>
-    <t>Nile Air NP-151</t>
-  </si>
-  <si>
-    <t>10-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-353</t>
-  </si>
-  <si>
-    <t>13-AUG-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-162</t>
-  </si>
-  <si>
-    <t>Nile Air NP-255</t>
-  </si>
-  <si>
-    <t>17-AUG-26</t>
-  </si>
-  <si>
-    <t>20-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-355</t>
-  </si>
-  <si>
-    <t>24-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-351</t>
-  </si>
-  <si>
-    <t>27-AUG-26</t>
-  </si>
-  <si>
-    <t>31-AUG-26</t>
-  </si>
-  <si>
-    <t>03-SEP-26</t>
-  </si>
-  <si>
-    <t>flyadeal F3-608</t>
-  </si>
-  <si>
-    <t>flyadeal F3-606</t>
-  </si>
-  <si>
-    <t>flyadeal F3-614</t>
-  </si>
-  <si>
-    <t>07-SEP-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-649</t>
-  </si>
-  <si>
-    <t>10-SEP-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-689</t>
-  </si>
-  <si>
-    <t>flynas XY-280</t>
-  </si>
-  <si>
-    <t>14-SEP-26</t>
-  </si>
-  <si>
-    <t>flynas XY-274</t>
-  </si>
-  <si>
     <t>17-SEP-26</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
   </si>
   <si>
     <t>24-SEP-26</t>
-  </si>
-  <si>
-    <t>24-NOV-26</t>
   </si>
 </sst>
 </file>
@@ -231,6 +225,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD4EDDA"/>
         <bgColor rgb="FFD4EDDA"/>
       </patternFill>
@@ -239,12 +239,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
         <bgColor rgb="FFF8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -595,12 +589,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="153.44140625" customWidth="1"/>
@@ -656,13 +650,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>13870</v>
+        <v>13692</v>
       </c>
       <c r="E2" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F2" s="2">
-        <v>-3577</v>
+        <v>-6949</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -682,22 +676,22 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D3" s="2">
-        <v>12464</v>
+        <v>13692</v>
       </c>
       <c r="E3" s="2">
-        <v>24628</v>
+        <v>20641</v>
       </c>
       <c r="F3" s="2">
-        <v>-12164</v>
+        <v>-6949</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -708,8 +702,8 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>15</v>
@@ -717,22 +711,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2">
-        <v>13693</v>
+        <v>13870</v>
       </c>
       <c r="E4" s="2">
-        <v>24628</v>
+        <v>20641</v>
       </c>
       <c r="F4" s="2">
-        <v>-10935</v>
+        <v>-6771</v>
       </c>
       <c r="G4" s="2">
         <v>30</v>
@@ -743,8 +737,8 @@
       <c r="I4" s="2">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
+      <c r="J4" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -752,7 +746,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -761,25 +755,25 @@
         <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>15631</v>
+        <v>12218</v>
       </c>
       <c r="E5" s="2">
-        <v>24628</v>
+        <v>17447</v>
       </c>
       <c r="F5" s="2">
-        <v>-8997</v>
+        <v>-5229</v>
       </c>
       <c r="G5" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -787,34 +781,34 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2">
-        <v>11932</v>
+        <v>12218</v>
       </c>
       <c r="E6" s="2">
-        <v>20642</v>
+        <v>17447</v>
       </c>
       <c r="F6" s="2">
-        <v>-8710</v>
+        <v>-5229</v>
       </c>
       <c r="G6" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2">
         <v>30</v>
       </c>
       <c r="I6" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -822,34 +816,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2">
-        <v>11932</v>
+        <v>13406</v>
       </c>
       <c r="E7" s="2">
-        <v>20642</v>
+        <v>17447</v>
       </c>
       <c r="F7" s="2">
-        <v>-8710</v>
+        <v>-4041</v>
       </c>
       <c r="G7" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2">
         <v>30</v>
       </c>
       <c r="I7" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -857,34 +851,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2">
+        <v>11153</v>
+      </c>
+      <c r="E8" s="2">
+        <v>20641</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-9488</v>
+      </c>
+      <c r="G8" s="2">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="D8" s="2">
-        <v>11932</v>
-      </c>
-      <c r="E8" s="2">
-        <v>20642</v>
-      </c>
-      <c r="F8" s="2">
-        <v>-8710</v>
-      </c>
-      <c r="G8" s="2">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -892,22 +886,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>11153</v>
       </c>
       <c r="E9" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F9" s="2">
-        <v>-6294</v>
+        <v>-9488</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
@@ -919,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -927,22 +921,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
         <v>11153</v>
       </c>
       <c r="E10" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F10" s="2">
-        <v>-6294</v>
+        <v>-9488</v>
       </c>
       <c r="G10" s="2">
         <v>30</v>
@@ -954,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -968,28 +962,28 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2">
-        <v>11153</v>
+        <v>10534</v>
       </c>
       <c r="E11" s="2">
-        <v>17447</v>
+        <v>20641</v>
       </c>
       <c r="F11" s="2">
-        <v>-6294</v>
+        <v>-10107</v>
       </c>
       <c r="G11" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2">
         <v>30</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -997,22 +991,22 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2">
         <v>11153</v>
       </c>
       <c r="E12" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F12" s="2">
-        <v>-9489</v>
+        <v>-9488</v>
       </c>
       <c r="G12" s="2">
         <v>30</v>
@@ -1023,8 +1017,8 @@
       <c r="I12" s="2">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>17</v>
+      <c r="J12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -1032,22 +1026,22 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2">
-        <v>11153</v>
+        <v>11221</v>
       </c>
       <c r="E13" s="2">
-        <v>20642</v>
+        <v>20641</v>
       </c>
       <c r="F13" s="2">
-        <v>-9489</v>
+        <v>-9420</v>
       </c>
       <c r="G13" s="2">
         <v>30</v>
@@ -1058,8 +1052,8 @@
       <c r="I13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>17</v>
+      <c r="J13" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1067,22 +1061,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2">
-        <v>11153</v>
+        <v>12218</v>
       </c>
       <c r="E14" s="2">
-        <v>20642</v>
+        <v>17447</v>
       </c>
       <c r="F14" s="2">
-        <v>-9489</v>
+        <v>-5229</v>
       </c>
       <c r="G14" s="2">
         <v>30</v>
@@ -1094,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1102,22 +1096,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2">
-        <v>11222</v>
+        <v>12218</v>
       </c>
       <c r="E15" s="2">
         <v>17447</v>
       </c>
       <c r="F15" s="2">
-        <v>-6225</v>
+        <v>-5229</v>
       </c>
       <c r="G15" s="2">
         <v>30</v>
@@ -1128,8 +1122,8 @@
       <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>26</v>
+      <c r="J15" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1137,34 +1131,34 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2">
-        <v>12218</v>
+        <v>14785</v>
       </c>
       <c r="E16" s="2">
         <v>17447</v>
       </c>
       <c r="F16" s="2">
-        <v>-5229</v>
+        <v>-2662</v>
       </c>
       <c r="G16" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1172,22 +1166,22 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2">
-        <v>12218</v>
+        <v>13692</v>
       </c>
       <c r="E17" s="2">
         <v>17447</v>
       </c>
       <c r="F17" s="2">
-        <v>-5229</v>
+        <v>-3755</v>
       </c>
       <c r="G17" s="2">
         <v>30</v>
@@ -1198,8 +1192,8 @@
       <c r="I17" s="2">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>14</v>
+      <c r="J17" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1207,22 +1201,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D18" s="2">
-        <v>12464</v>
+        <v>13692</v>
       </c>
       <c r="E18" s="2">
         <v>17447</v>
       </c>
       <c r="F18" s="2">
-        <v>-4983</v>
+        <v>-3755</v>
       </c>
       <c r="G18" s="2">
         <v>30</v>
@@ -1233,8 +1227,8 @@
       <c r="I18" s="2">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>14</v>
+      <c r="J18" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1242,22 +1236,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E19" s="2">
         <v>17447</v>
       </c>
       <c r="F19" s="2">
-        <v>-3754</v>
+        <v>-3755</v>
       </c>
       <c r="G19" s="2">
         <v>30</v>
@@ -1268,8 +1262,8 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>14</v>
+      <c r="J19" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1277,7 +1271,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1286,25 +1280,25 @@
         <v>19</v>
       </c>
       <c r="D20" s="2">
-        <v>15973</v>
+        <v>13692</v>
       </c>
       <c r="E20" s="2">
         <v>17447</v>
       </c>
       <c r="F20" s="2">
-        <v>-1474</v>
+        <v>-3755</v>
       </c>
       <c r="G20" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2">
         <v>30</v>
       </c>
       <c r="I20" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1312,22 +1306,22 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E21" s="2">
-        <v>20642</v>
+        <v>17447</v>
       </c>
       <c r="F21" s="2">
-        <v>-6949</v>
+        <v>-3755</v>
       </c>
       <c r="G21" s="2">
         <v>30</v>
@@ -1338,8 +1332,8 @@
       <c r="I21" s="2">
         <v>0</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>26</v>
+      <c r="J21" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1347,22 +1341,22 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D22" s="2">
-        <v>13693</v>
+        <v>13692</v>
       </c>
       <c r="E22" s="2">
-        <v>20642</v>
+        <v>17447</v>
       </c>
       <c r="F22" s="2">
-        <v>-6949</v>
+        <v>-3755</v>
       </c>
       <c r="G22" s="2">
         <v>30</v>
@@ -1373,8 +1367,8 @@
       <c r="I22" s="2">
         <v>0</v>
       </c>
-      <c r="J22" s="5" t="s">
-        <v>26</v>
+      <c r="J22" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1382,22 +1376,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D23" s="2">
-        <v>13693</v>
+        <v>12218</v>
       </c>
       <c r="E23" s="2">
-        <v>20642</v>
+        <v>15044</v>
       </c>
       <c r="F23" s="2">
-        <v>-6949</v>
+        <v>-2826</v>
       </c>
       <c r="G23" s="2">
         <v>30</v>
@@ -1408,8 +1402,8 @@
       <c r="I23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>26</v>
+      <c r="J23" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1417,13 +1411,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D24" s="2">
         <v>12218</v>
@@ -1443,8 +1437,8 @@
       <c r="I24" s="2">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>14</v>
+      <c r="J24" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1452,13 +1446,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D25" s="2">
         <v>12218</v>
@@ -1478,8 +1472,8 @@
       <c r="I25" s="2">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>14</v>
+      <c r="J25" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>15</v>
@@ -1487,22 +1481,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D26" s="2">
-        <v>12218</v>
+        <v>11221</v>
       </c>
       <c r="E26" s="2">
         <v>15044</v>
       </c>
       <c r="F26" s="2">
-        <v>-2826</v>
+        <v>-3823</v>
       </c>
       <c r="G26" s="2">
         <v>30</v>
@@ -1513,8 +1507,8 @@
       <c r="I26" s="2">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>14</v>
+      <c r="J26" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1522,22 +1516,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D27" s="2">
-        <v>11222</v>
+        <v>12218</v>
       </c>
       <c r="E27" s="2">
         <v>15044</v>
       </c>
       <c r="F27" s="2">
-        <v>-3822</v>
+        <v>-2826</v>
       </c>
       <c r="G27" s="2">
         <v>30</v>
@@ -1548,8 +1542,8 @@
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>14</v>
+      <c r="J27" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>15</v>
@@ -1557,13 +1551,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2">
         <v>12218</v>
@@ -1583,8 +1577,8 @@
       <c r="I28" s="2">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>14</v>
+      <c r="J28" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1598,16 +1592,16 @@
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D29" s="2">
-        <v>12218</v>
+        <v>11153</v>
       </c>
       <c r="E29" s="2">
         <v>15044</v>
       </c>
       <c r="F29" s="2">
-        <v>-2826</v>
+        <v>-3891</v>
       </c>
       <c r="G29" s="2">
         <v>30</v>
@@ -1618,8 +1612,8 @@
       <c r="I29" s="2">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>14</v>
+      <c r="J29" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>15</v>
@@ -1627,22 +1621,22 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D30" s="2">
-        <v>11153</v>
+        <v>11221</v>
       </c>
       <c r="E30" s="2">
         <v>15044</v>
       </c>
       <c r="F30" s="2">
-        <v>-3891</v>
+        <v>-3823</v>
       </c>
       <c r="G30" s="2">
         <v>30</v>
@@ -1653,8 +1647,8 @@
       <c r="I30" s="2">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>14</v>
+      <c r="J30" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>15</v>
@@ -1662,22 +1656,22 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D31" s="2">
-        <v>11222</v>
+        <v>12218</v>
       </c>
       <c r="E31" s="2">
         <v>15044</v>
       </c>
       <c r="F31" s="2">
-        <v>-3822</v>
+        <v>-2826</v>
       </c>
       <c r="G31" s="2">
         <v>30</v>
@@ -1688,8 +1682,8 @@
       <c r="I31" s="2">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>14</v>
+      <c r="J31" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>15</v>
@@ -1703,28 +1697,28 @@
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D32" s="2">
-        <v>12218</v>
+        <v>9815</v>
       </c>
       <c r="E32" s="2">
-        <v>15044</v>
+        <v>17447</v>
       </c>
       <c r="F32" s="2">
-        <v>-2826</v>
+        <v>-7632</v>
       </c>
       <c r="G32" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1732,7 +1726,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>12</v>
@@ -1741,25 +1735,25 @@
         <v>41</v>
       </c>
       <c r="D33" s="2">
-        <v>13229</v>
+        <v>9815</v>
       </c>
       <c r="E33" s="2">
         <v>17447</v>
       </c>
       <c r="F33" s="2">
-        <v>-4218</v>
+        <v>-7632</v>
       </c>
       <c r="G33" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2">
         <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1767,7 +1761,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>12</v>
@@ -1776,25 +1770,25 @@
         <v>42</v>
       </c>
       <c r="D34" s="2">
-        <v>13229</v>
+        <v>9815</v>
       </c>
       <c r="E34" s="2">
         <v>17447</v>
       </c>
       <c r="F34" s="2">
-        <v>-4218</v>
+        <v>-7632</v>
       </c>
       <c r="G34" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2">
         <v>30</v>
       </c>
       <c r="I34" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1802,7 +1796,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
@@ -1811,13 +1805,13 @@
         <v>43</v>
       </c>
       <c r="D35" s="2">
-        <v>13229</v>
+        <v>16327</v>
       </c>
       <c r="E35" s="2">
         <v>17447</v>
       </c>
       <c r="F35" s="2">
-        <v>-4218</v>
+        <v>-1120</v>
       </c>
       <c r="G35" s="2">
         <v>40</v>
@@ -1828,8 +1822,8 @@
       <c r="I35" s="2">
         <v>-10</v>
       </c>
-      <c r="J35" s="5" t="s">
-        <v>26</v>
+      <c r="J35" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1843,7 +1837,7 @@
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2">
         <v>7768</v>
@@ -1863,8 +1857,8 @@
       <c r="I36" s="2">
         <v>15</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>14</v>
+      <c r="J36" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -1878,7 +1872,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D37" s="2">
         <v>11467</v>
@@ -1898,8 +1892,8 @@
       <c r="I37" s="2">
         <v>-16</v>
       </c>
-      <c r="J37" s="5" t="s">
-        <v>26</v>
+      <c r="J37" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -1913,16 +1907,16 @@
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D38" s="2">
-        <v>11850</v>
+        <v>11849</v>
       </c>
       <c r="E38" s="2">
         <v>15044</v>
       </c>
       <c r="F38" s="2">
-        <v>-3194</v>
+        <v>-3195</v>
       </c>
       <c r="G38" s="2">
         <v>46</v>
@@ -1933,8 +1927,8 @@
       <c r="I38" s="2">
         <v>-16</v>
       </c>
-      <c r="J38" s="5" t="s">
-        <v>26</v>
+      <c r="J38" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -1948,7 +1942,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D39" s="2">
         <v>11467</v>
@@ -1968,8 +1962,8 @@
       <c r="I39" s="2">
         <v>-16</v>
       </c>
-      <c r="J39" s="5" t="s">
-        <v>26</v>
+      <c r="J39" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>15</v>
@@ -1983,16 +1977,16 @@
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2">
-        <v>11850</v>
+        <v>11849</v>
       </c>
       <c r="E40" s="2">
         <v>15044</v>
       </c>
       <c r="F40" s="2">
-        <v>-3194</v>
+        <v>-3195</v>
       </c>
       <c r="G40" s="2">
         <v>46</v>
@@ -2003,8 +1997,8 @@
       <c r="I40" s="2">
         <v>-16</v>
       </c>
-      <c r="J40" s="5" t="s">
-        <v>26</v>
+      <c r="J40" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -2018,16 +2012,16 @@
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D41" s="2">
-        <v>11850</v>
+        <v>11849</v>
       </c>
       <c r="E41" s="2">
         <v>15044</v>
       </c>
       <c r="F41" s="2">
-        <v>-3194</v>
+        <v>-3195</v>
       </c>
       <c r="G41" s="2">
         <v>46</v>
@@ -2038,8 +2032,8 @@
       <c r="I41" s="2">
         <v>-16</v>
       </c>
-      <c r="J41" s="5" t="s">
-        <v>26</v>
+      <c r="J41" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>15</v>
@@ -2047,31 +2041,31 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2">
-        <v>16328</v>
+        <v>8232</v>
       </c>
       <c r="E42" s="2">
         <v>15044</v>
       </c>
       <c r="F42" s="2">
-        <v>1284</v>
+        <v>-6812</v>
       </c>
       <c r="G42" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2">
         <v>30</v>
       </c>
       <c r="I42" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>14</v>
@@ -2082,34 +2076,34 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D43" s="2">
-        <v>8232</v>
+        <v>9337</v>
       </c>
       <c r="E43" s="2">
         <v>15044</v>
       </c>
       <c r="F43" s="2">
-        <v>-6812</v>
+        <v>-5707</v>
       </c>
       <c r="G43" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H43" s="2">
         <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>0</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>26</v>
+        <v>-10</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2117,22 +2111,22 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="D44" s="2">
-        <v>9338</v>
+        <v>10020</v>
       </c>
       <c r="E44" s="2">
         <v>15044</v>
       </c>
       <c r="F44" s="2">
-        <v>-5706</v>
+        <v>-5024</v>
       </c>
       <c r="G44" s="2">
         <v>40</v>
@@ -2143,8 +2137,8 @@
       <c r="I44" s="2">
         <v>-10</v>
       </c>
-      <c r="J44" s="5" t="s">
-        <v>26</v>
+      <c r="J44" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>15</v>
@@ -2152,7 +2146,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
@@ -2161,25 +2155,25 @@
         <v>21</v>
       </c>
       <c r="D45" s="2">
-        <v>10020</v>
+        <v>8873</v>
       </c>
       <c r="E45" s="2">
         <v>15044</v>
       </c>
       <c r="F45" s="2">
-        <v>-5024</v>
+        <v>-6171</v>
       </c>
       <c r="G45" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2">
         <v>30</v>
       </c>
       <c r="I45" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>15</v>
@@ -2187,22 +2181,22 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D46" s="2">
-        <v>8873</v>
+        <v>9269</v>
       </c>
       <c r="E46" s="2">
         <v>15044</v>
       </c>
       <c r="F46" s="2">
-        <v>-6171</v>
+        <v>-5775</v>
       </c>
       <c r="G46" s="2">
         <v>46</v>
@@ -2213,8 +2207,8 @@
       <c r="I46" s="2">
         <v>-16</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>17</v>
+      <c r="J46" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>15</v>
@@ -2222,22 +2216,22 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D47" s="2">
-        <v>9269</v>
+        <v>9378</v>
       </c>
       <c r="E47" s="2">
         <v>15044</v>
       </c>
       <c r="F47" s="2">
-        <v>-5775</v>
+        <v>-5666</v>
       </c>
       <c r="G47" s="2">
         <v>46</v>
@@ -2248,8 +2242,8 @@
       <c r="I47" s="2">
         <v>-16</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>26</v>
+      <c r="J47" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2257,34 +2251,34 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D48" s="2">
-        <v>9379</v>
+        <v>14962</v>
       </c>
       <c r="E48" s="2">
         <v>15044</v>
       </c>
       <c r="F48" s="2">
-        <v>-5665</v>
+        <v>-82</v>
       </c>
       <c r="G48" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H48" s="2">
         <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>26</v>
+        <v>-10</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2298,28 +2292,28 @@
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D49" s="2">
-        <v>14962</v>
+        <v>8068</v>
       </c>
       <c r="E49" s="2">
-        <v>15044</v>
+        <v>9856</v>
       </c>
       <c r="F49" s="2">
-        <v>-82</v>
+        <v>-1788</v>
       </c>
       <c r="G49" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2">
         <v>30</v>
       </c>
       <c r="I49" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2327,22 +2321,22 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D50" s="2">
-        <v>8068</v>
+        <v>8300</v>
       </c>
       <c r="E50" s="2">
         <v>9856</v>
       </c>
       <c r="F50" s="2">
-        <v>-1788</v>
+        <v>-1556</v>
       </c>
       <c r="G50" s="2">
         <v>46</v>
@@ -2353,8 +2347,8 @@
       <c r="I50" s="2">
         <v>-16</v>
       </c>
-      <c r="J50" s="3" t="s">
-        <v>14</v>
+      <c r="J50" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>15</v>
@@ -2362,13 +2356,13 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D51" s="2">
         <v>8300</v>
@@ -2388,8 +2382,8 @@
       <c r="I51" s="2">
         <v>-16</v>
       </c>
-      <c r="J51" s="3" t="s">
-        <v>14</v>
+      <c r="J51" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>15</v>
@@ -2403,16 +2397,16 @@
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D52" s="2">
-        <v>8300</v>
+        <v>8068</v>
       </c>
       <c r="E52" s="2">
-        <v>9856</v>
+        <v>9037</v>
       </c>
       <c r="F52" s="2">
-        <v>-1556</v>
+        <v>-969</v>
       </c>
       <c r="G52" s="2">
         <v>46</v>
@@ -2423,8 +2417,8 @@
       <c r="I52" s="2">
         <v>-16</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>14</v>
+      <c r="J52" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>15</v>
@@ -2432,7 +2426,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>12</v>
@@ -2441,13 +2435,13 @@
         <v>45</v>
       </c>
       <c r="D53" s="2">
-        <v>8068</v>
+        <v>8300</v>
       </c>
       <c r="E53" s="2">
         <v>9037</v>
       </c>
       <c r="F53" s="2">
-        <v>-969</v>
+        <v>-737</v>
       </c>
       <c r="G53" s="2">
         <v>46</v>
@@ -2458,80 +2452,10 @@
       <c r="I53" s="2">
         <v>-16</v>
       </c>
-      <c r="J53" s="3" t="s">
-        <v>14</v>
+      <c r="J53" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" s="2">
-        <v>8300</v>
-      </c>
-      <c r="E54" s="2">
-        <v>9037</v>
-      </c>
-      <c r="F54" s="2">
-        <v>-737</v>
-      </c>
-      <c r="G54" s="2">
-        <v>46</v>
-      </c>
-      <c r="H54" s="2">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D55" s="2">
-        <v>8546</v>
-      </c>
-      <c r="E55" s="2">
-        <v>9037</v>
-      </c>
-      <c r="F55" s="2">
-        <v>-491</v>
-      </c>
-      <c r="G55" s="2">
-        <v>40</v>
-      </c>
-      <c r="H55" s="2">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K55" s="2" t="s">
         <v>15</v>
       </c>
     </row>
